--- a/data/mwe_list.xlsx
+++ b/data/mwe_list.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/mwe_list.xlsx
+++ b/data/mwe_list.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/mwe_list.xlsx
+++ b/data/mwe_list.xlsx
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21">
@@ -748,31 +748,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>hype</t>
+          <t>assistenza</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>inesistente</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>assistenza</t>
+          <t>hype</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>inesistente</t>
+          <t>next</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
